--- a/BWI/bestwine_output/bestwine_Bahrain.xlsx
+++ b/BWI/bestwine_output/bestwine_Bahrain.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
     <font>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +56,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,13 +74,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1806,6 +1815,75 @@
       <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Gbi Express</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Gbi Express</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>60265</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>P. O. Box 26535</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gbiexpress.com</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>info@gbiexpress.com</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>+973 1710 4964</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
